--- a/population-projection/src/main/resources/mortality_tables/Russian-Empire/novoselsky_1896_1897.xlsx
+++ b/population-projection/src/main/resources/mortality_tables/Russian-Empire/novoselsky_1896_1897.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\mortality_tables\Russian-Empire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959B2B58-A0B6-41D3-9051-0739C2558D3F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898B3C99-7993-4B98-AE26-0C1019F6392E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,20 @@
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
     <sheet name="Data" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
   <si>
     <t>возраст x</t>
   </si>
@@ -105,6 +113,15 @@
   </si>
   <si>
     <t>Так как данные об умерших не содержали Киргизской и Калмыцкой степей Астраханской губернии, а в итогах живущих по 50 губерниям Европейской России эти территории учитывались, из чисел живущих по возрастам были вычтены жители этих степей (общее число 343,369).</t>
+  </si>
+  <si>
+    <t>Добавочное исправление</t>
+  </si>
+  <si>
+    <t>Они заполнены вычислением lx × qx, т.е. l100 × q100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Значения dx для возраста 100 в издании оставлены пустыми. </t>
   </si>
 </sst>
 </file>
@@ -232,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -295,6 +312,9 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -318,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NovoselskyLifeTable" displayName="NovoselskyLifeTable" ref="A3:G104">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NovoselskyLifeTable" displayName="NovoselskyLifeTable" ref="A3:G105">
   <tableColumns count="7">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="возраст x"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="lₓ"/>
@@ -481,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -563,6 +583,19 @@
     <row r="10" spans="1:2">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" s="22" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7182,7 +7215,9 @@
       <c r="B104" s="1">
         <v>331</v>
       </c>
-      <c r="C104" s="1"/>
+      <c r="C104" s="1">
+        <v>54</v>
+      </c>
       <c r="D104" s="2">
         <v>0.16302</v>
       </c>
@@ -7201,7 +7236,9 @@
       <c r="J104" s="7">
         <v>384</v>
       </c>
-      <c r="K104" s="7"/>
+      <c r="K104" s="7">
+        <v>59</v>
+      </c>
       <c r="L104" s="8">
         <v>0.15373999999999999</v>
       </c>
@@ -7220,7 +7257,9 @@
       <c r="R104" s="11">
         <v>359</v>
       </c>
-      <c r="S104" s="11"/>
+      <c r="S104" s="11">
+        <v>57</v>
+      </c>
       <c r="T104" s="12">
         <v>0.15808</v>
       </c>
